--- a/technology_surveys/050_tech_gadget_consumer_preference_poll--technology_surveys.xlsx
+++ b/technology_surveys/050_tech_gadget_consumer_preference_poll--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'price'}</t>
+          <t>price</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Price'}</t>
+          <t>Price</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'camera'}</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Camera'}</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'battery'}</t>
+          <t>battery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Battery'}</t>
+          <t>Battery</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'storage'}</t>
+          <t>storage</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Storage'}</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'performance'}</t>
+          <t>performance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Performance'}</t>
+          <t>Performance</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'retail'}</t>
+          <t>retail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Retail'}</t>
+          <t>Retail</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'gps'}</t>
+          <t>gps</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'GPS'}</t>
+          <t>GPS</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'touch_screen'}</t>
+          <t>touch_screen</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Touch Screen'}</t>
+          <t>Touch Screen</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'camera'}</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Camera'}</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'headphone_jack'}</t>
+          <t>headphone_jack</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Headphone Jack'}</t>
+          <t>Headphone Jack</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'microphone'}</t>
+          <t>microphone</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Microphone'}</t>
+          <t>Microphone</t>
         </is>
       </c>
     </row>
